--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AISC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Raw Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ratios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AISC" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,7 +583,7 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.36</v>
+        <v>17.56</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.39</v>
+        <v>45.92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.86</v>
+        <v>16.02</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.88</v>
+        <v>17.08</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.35</v>
+        <v>8.43</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.48</v>
+        <v>8.56</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.09</v>
+        <v>10.16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.92</v>
+        <v>27.28</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.43</v>
+        <v>6.51</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.03</v>
+        <v>61.13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.36</v>
+        <v>17.555</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8571.84</v>
+        <v>8668.125184</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.4</v>
+        <v>45.92</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19129.290752</v>
+        <v>19348.391936</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.865</v>
+        <v>16.0201</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10640.851968</v>
+        <v>10744.879104</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.875</v>
+        <v>17.075</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17390.270464</v>
+        <v>17596.377088</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.355</v>
+        <v>8.425000000000001</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2473.654784</v>
+        <v>2494.379776</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.475</v>
+        <v>8.555</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2567.563776</v>
+        <v>2591.80032</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.085</v>
+        <v>10.165</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2230.82752</v>
+        <v>2248.523776</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>26.92</v>
+        <v>27.28</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3858.975232</v>
+        <v>3910.580992</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.5501394</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.435</v>
+        <v>6.51</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1127.869056</v>
+        <v>1141.0144</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -583,7 +583,7 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.56</v>
+        <v>17.82</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.92</v>
+        <v>46.29</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16.02</v>
+        <v>16.33</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.08</v>
+        <v>17.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.43</v>
+        <v>8.56</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.56</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.16</v>
+        <v>10.27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.28</v>
+        <v>27.76</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.51</v>
+        <v>6.57</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.13</v>
+        <v>61.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.555</v>
+        <v>17.82</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8668.125184</v>
+        <v>8798.973952</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.92</v>
+        <v>46.29</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19348.391936</v>
+        <v>19504.29184</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.0201</v>
+        <v>16.33</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10744.879104</v>
+        <v>10952.732672</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10134.457344</v>
+        <v>10630.785024</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.075</v>
+        <v>17.3</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17596.377088</v>
+        <v>17828.247552</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.425000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2494.379776</v>
+        <v>2534.349056</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2479.613696</v>
+        <v>2544.749056</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.555</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2591.80032</v>
+        <v>2641.788416</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2130.493184</v>
+        <v>2242.587392</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.165</v>
+        <v>10.27</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2248.523776</v>
+        <v>2271.750144</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2086.01856</v>
+        <v>2132.47104</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.28</v>
+        <v>27.76</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3910.580992</v>
+        <v>3979.388928</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.5501394</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.51</v>
+        <v>6.57</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1141.0144</v>
+        <v>1151.530624</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-02 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-03 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37.24</v>
+        <v>38.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.76</v>
+        <v>29.32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.6</v>
+        <v>62.81</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-02 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-03 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8009.183232</v>
+        <v>8394.323456</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5039,7 +5039,7 @@
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17910.44608</v>
+        <v>18736.29184</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.24</v>
+        <v>38.25</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27441.917952</v>
+        <v>28186.179584</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25978.208256</v>
+        <v>26722.469888</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5144,7 +5144,7 @@
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17040.861184</v>
+        <v>17827.088384</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.76</v>
+        <v>29.32</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3979.388928</v>
+        <v>4203.0144</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.5501394</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3789.036288</v>
+        <v>4141.676544</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5319,7 +5319,7 @@
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>952.0849920000001</v>
+        <v>987.824128</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-03 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-06 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.82</v>
+        <v>17.31</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46.29</v>
+        <v>45.02</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>38.25</v>
+        <v>38.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16.33</v>
+        <v>16.46</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.3</v>
+        <v>16.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.56</v>
+        <v>8.51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.27</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>29.32</v>
+        <v>28.24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>62.81</v>
+        <v>62.46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-03 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-06 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.82</v>
+        <v>17.31</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8798.973952</v>
+        <v>8547.150847999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8394.323456</v>
+        <v>8142.501376</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>46.29</v>
+        <v>45.02</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19504.29184</v>
+        <v>18969.178112</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>38.25</v>
+        <v>38.9</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>28186.179584</v>
+        <v>28665.161728</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.33</v>
+        <v>16.46</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10952.732672</v>
+        <v>11039.925248</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.3</v>
+        <v>16.99</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17828.247552</v>
+        <v>17508.78208</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17827.088384</v>
+        <v>17506.390016</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.56</v>
+        <v>8.51</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2534.349056</v>
+        <v>2519.5456</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.720000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2641.788416</v>
+        <v>2629.670144</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.27</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2271.750144</v>
+        <v>2203.177216</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>29.32</v>
+        <v>28.24</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4203.0144</v>
+        <v>4048.196864</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.5501394</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1151.530624</v>
+        <v>1153.283328</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>987.824128</v>
+        <v>989.526016</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-06 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-07 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.31</v>
+        <v>16.45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.02</v>
+        <v>44.16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>38.9</v>
+        <v>36.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16.46</v>
+        <v>15.56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.99</v>
+        <v>16.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.51</v>
+        <v>8.02</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.68</v>
+        <v>8.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>28.24</v>
+        <v>26.67</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.58</v>
+        <v>6.07</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>62.46</v>
+        <v>60.33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-06 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-07 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.31</v>
+        <v>16.45</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8547.150847999999</v>
+        <v>8122.509824</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8142.501376</v>
+        <v>7717.859328</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.02</v>
+        <v>44.16</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18969.178112</v>
+        <v>18606.81728</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18736.29184</v>
+        <v>18201.176064</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>38.9</v>
+        <v>36.55</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>28665.161728</v>
+        <v>26933.458944</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>26722.469888</v>
+        <v>26228.750336</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.46</v>
+        <v>15.56</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11039.925248</v>
+        <v>10436.28544</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10630.785024</v>
+        <v>10717.9776</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.99</v>
+        <v>16.04</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17508.78208</v>
+        <v>16529.774592</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17506.390016</v>
+        <v>16523.606016</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.51</v>
+        <v>8.02</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2519.5456</v>
+        <v>2374.471936</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2544.749056</v>
+        <v>2529.9456</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.68</v>
+        <v>8.42</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2629.670144</v>
+        <v>2550.901248</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2242.587392</v>
+        <v>2230.46912</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.960000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2203.177216</v>
+        <v>2072.667648</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2132.47104</v>
+        <v>2063.89824</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>28.24</v>
+        <v>26.67</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4048.196864</v>
+        <v>3823.137792</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.5501394</v>
+        <v>4.551742</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4141.676544</v>
+        <v>3986.859008</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.58</v>
+        <v>6.07</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1153.283328</v>
+        <v>1063.895168</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>989.526016</v>
+        <v>902.730816</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-07 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-08 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.45</v>
+        <v>15.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.16</v>
+        <v>42.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>36.55</v>
+        <v>34.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.56</v>
+        <v>15.09</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.04</v>
+        <v>15.24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.02</v>
+        <v>7.72</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -769,14 +769,14 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.67</v>
+        <v>27.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.07</v>
+        <v>5.73</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.33</v>
+        <v>58.74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-07 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-08 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.45</v>
+        <v>15.8</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8122.509824</v>
+        <v>7801.55904</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7717.859328</v>
+        <v>7396.909056</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.16</v>
+        <v>42.6</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18606.81728</v>
+        <v>17949.509632</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18201.176064</v>
+        <v>17838.815232</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>36.55</v>
+        <v>34.55</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26933.458944</v>
+        <v>25459.673088</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>26228.750336</v>
+        <v>25469.751296</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.56</v>
+        <v>15.09</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10436.28544</v>
+        <v>10121.050112</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10717.9776</v>
+        <v>10114.335744</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.04</v>
+        <v>15.24</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16529.774592</v>
+        <v>15705.346048</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16523.606016</v>
+        <v>15695.996928</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.02</v>
+        <v>7.72</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2374.471936</v>
+        <v>2285.6512</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2529.9456</v>
+        <v>2384.87168</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2550.901248</v>
+        <v>2463.043584</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2230.46912</v>
+        <v>2151.700224</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.369999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2072.667648</v>
+        <v>2015.154944</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2063.89824</v>
+        <v>1933.3888</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>26.67</v>
+        <v>27.05</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3823.137792</v>
+        <v>3877.610496</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.551742</v>
+        <v>4.5501394</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3986.859008</v>
+        <v>3761.79968</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.07</v>
+        <v>5.73</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1063.895168</v>
+        <v>1004.302976</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>902.730816</v>
+        <v>844.867392</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-08 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-09 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.8</v>
+        <v>17.16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42.6</v>
+        <v>44.12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34.55</v>
+        <v>35.23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.09</v>
+        <v>15.79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.24</v>
+        <v>16.02</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.72</v>
+        <v>8.24</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.35</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.05</v>
+        <v>28.14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.73</v>
+        <v>6.15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.74</v>
+        <v>60.44</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-08 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-09 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.8</v>
+        <v>17.16</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7801.55904</v>
+        <v>8473.085951999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7396.909056</v>
+        <v>8068.435968</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>42.6</v>
+        <v>44.12</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17949.509632</v>
+        <v>18589.96224</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17838.815232</v>
+        <v>17181.509632</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34.55</v>
+        <v>35.23</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25459.673088</v>
+        <v>25960.759296</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25469.751296</v>
+        <v>24497.051648</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.09</v>
+        <v>15.79</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10121.050112</v>
+        <v>10590.548992</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10114.335744</v>
+        <v>9799.10144</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.24</v>
+        <v>16.02</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15705.346048</v>
+        <v>16509.16352</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15695.996928</v>
+        <v>16502.915072</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.72</v>
+        <v>8.24</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2285.6512</v>
+        <v>2439.606784</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2384.87168</v>
+        <v>2296.0512</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.130000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2463.043584</v>
+        <v>2596.344576</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2151.700224</v>
+        <v>2063.84256</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.109999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2015.154944</v>
+        <v>2121.332224</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1933.3888</v>
+        <v>1875.876096</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.05</v>
+        <v>28.14</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3877.610496</v>
+        <v>4033.861632</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.5501394</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3761.79968</v>
+        <v>3816.27264</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.73</v>
+        <v>6.15</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1004.302976</v>
+        <v>1077.9168</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>844.867392</v>
+        <v>916.345792</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-09 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-10 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.16</v>
+        <v>16.95</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.12</v>
+        <v>43.67</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.23</v>
+        <v>35.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.79</v>
+        <v>15.82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.02</v>
+        <v>15.98</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.24</v>
+        <v>8.08</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.57</v>
+        <v>8.52</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -769,14 +769,14 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.59</v>
+        <v>9.52</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>28.14</v>
+        <v>28.68</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.44</v>
+        <v>60.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-09 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-10 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.16</v>
+        <v>16.95</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8473.085951999999</v>
+        <v>8369.394688</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8068.435968</v>
+        <v>7964.744192</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.12</v>
+        <v>43.67</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18589.96224</v>
+        <v>18400.354304</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17181.509632</v>
+        <v>17821.96224</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.23</v>
+        <v>35.6</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25960.759296</v>
+        <v>26233.409536</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>24497.051648</v>
+        <v>25513.96352</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.79</v>
+        <v>15.82</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10590.548992</v>
+        <v>10610.669568</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9799.10144</v>
+        <v>10268.60032</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.02</v>
+        <v>15.98</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16509.16352</v>
+        <v>16467.941376</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.24</v>
+        <v>8.08</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2439.606784</v>
+        <v>2392.235776</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2296.0512</v>
+        <v>2450.00704</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.57</v>
+        <v>8.52</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2596.344576</v>
+        <v>2581.197056</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2063.84256</v>
+        <v>2197.143808</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.59</v>
+        <v>9.52</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2121.332224</v>
+        <v>2105.848192</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1875.876096</v>
+        <v>1982.053248</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>28.14</v>
+        <v>28.68</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4033.861632</v>
+        <v>4111.270656</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.5501394</v>
+        <v>4.541204</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3816.27264</v>
+        <v>3972.524032</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1077.9168</v>
+        <v>1060.38976</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>916.345792</v>
+        <v>899.327104</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-10 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-13 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.95</v>
+        <v>16.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43.67</v>
+        <v>42.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.6</v>
+        <v>36.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.82</v>
+        <v>15.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.98</v>
+        <v>15.59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.08</v>
+        <v>7.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.52</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.52</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>28.68</v>
+        <v>27.06</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.05</v>
+        <v>5.74</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.3</v>
+        <v>57.83</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-10 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-13 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.95</v>
+        <v>16.4</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8369.394688</v>
+        <v>8097.820672</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>43.67</v>
+        <v>42.7</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18400.354304</v>
+        <v>17991.645184</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17821.96224</v>
+        <v>17632.354304</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5074,7 +5074,7 @@
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25513.96352</v>
+        <v>25138.149376</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.82</v>
+        <v>15.25</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10610.669568</v>
+        <v>10228.364288</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10268.60032</v>
+        <v>9906.415616</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.98</v>
+        <v>15.59</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16467.941376</v>
+        <v>16066.033664</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16502.915072</v>
+        <v>16461.535232</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.08</v>
+        <v>7.84</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2392.235776</v>
+        <v>2321.179392</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2450.00704</v>
+        <v>2331.579392</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.52</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2581.197056</v>
+        <v>2535.753216</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2197.143808</v>
+        <v>2136.55232</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.52</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2105.848192</v>
+        <v>2039.48736</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1982.053248</v>
+        <v>1900.208384</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>28.68</v>
+        <v>27.06</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4111.270656</v>
+        <v>3879.044096</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.541204</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3972.524032</v>
+        <v>4049.9328</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.05</v>
+        <v>5.74</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1060.38976</v>
+        <v>1006.055616</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-13 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-14 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.4</v>
+        <v>16.93</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42.7</v>
+        <v>43.51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>36.1</v>
+        <v>34.85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.59</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.84</v>
+        <v>8.08</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.06</v>
+        <v>28.14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.74</v>
+        <v>5.98</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.83</v>
+        <v>59.01</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-13 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-14 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.4</v>
+        <v>16.93</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8097.820672</v>
+        <v>8359.51872</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7964.744192</v>
+        <v>7693.170688</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>42.7</v>
+        <v>43.51</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17991.645184</v>
+        <v>18332.93824</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17632.354304</v>
+        <v>17223.645184</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.6</v>
+        <v>34.85</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26233.409536</v>
+        <v>25680.740352</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25138.149376</v>
+        <v>24143.341568</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10228.364288</v>
+        <v>10396.04224</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9906.415616</v>
+        <v>10074.093568</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.59</v>
+        <v>16</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16066.033664</v>
+        <v>16488.552448</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16461.535232</v>
+        <v>16058.07616</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.84</v>
+        <v>8.08</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2321.179392</v>
+        <v>2392.235776</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2331.579392</v>
+        <v>2402.636032</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2535.753216</v>
+        <v>2578.167296</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2136.55232</v>
+        <v>2178.966272</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.220000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2039.48736</v>
+        <v>2074.879744</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1900.208384</v>
+        <v>1935.600768</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.06</v>
+        <v>28.14</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3879.044096</v>
+        <v>4033.861632</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.541204</v>
+        <v>4.54309</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4049.9328</v>
+        <v>3817.70624</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.74</v>
+        <v>5.98</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1006.055616</v>
+        <v>1048.120704</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>899.327104</v>
+        <v>846.56928</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-14 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-15 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.93</v>
+        <v>16.84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43.51</v>
+        <v>43.57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34.85</v>
+        <v>33.76</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.5</v>
+        <v>15.46</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16</v>
+        <v>15.91</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.08</v>
+        <v>7.96</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.51</v>
+        <v>8.48</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>28.14</v>
+        <v>27.72</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.98</v>
+        <v>5.93</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>59.01</v>
+        <v>58.15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-14 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-15 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.93</v>
+        <v>16.84</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8359.51872</v>
+        <v>8315.079680000001</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7693.170688</v>
+        <v>7954.868736</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>43.51</v>
+        <v>43.57</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18332.93824</v>
+        <v>18358.2208</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17223.645184</v>
+        <v>17564.93824</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34.85</v>
+        <v>33.76</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25680.740352</v>
+        <v>24877.524992</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>24143.341568</v>
+        <v>24217.030656</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.5</v>
+        <v>15.46</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10396.04224</v>
+        <v>10369.21344</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10074.093568</v>
+        <v>10047.264768</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16</v>
+        <v>15.91</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16488.552448</v>
+        <v>16395.804672</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16058.07616</v>
+        <v>16482.225152</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.08</v>
+        <v>7.96</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2392.235776</v>
+        <v>2356.707584</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2402.636032</v>
+        <v>2367.107584</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.51</v>
+        <v>8.48</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2578.167296</v>
+        <v>2569.078528</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2178.966272</v>
+        <v>2169.87776</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2074.879744</v>
+        <v>2063.81952</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1935.600768</v>
+        <v>1924.540672</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>28.14</v>
+        <v>27.72</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4033.861632</v>
+        <v>3973.654784</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.54309</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3817.70624</v>
+        <v>3972.524032</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.98</v>
+        <v>5.93</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1048.120704</v>
+        <v>1039.35712</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>846.56928</v>
+        <v>887.4140159999999</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-15 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-16 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.84</v>
+        <v>15.88</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43.57</v>
+        <v>41.98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.76</v>
+        <v>34.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.46</v>
+        <v>14.52</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.91</v>
+        <v>14.79</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.96</v>
+        <v>7.49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.48</v>
+        <v>8.23</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.33</v>
+        <v>8.82</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.72</v>
+        <v>26.33</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.93</v>
+        <v>5.51</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.15</v>
+        <v>55.81</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-15 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-16 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.84</v>
+        <v>15.88</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8315.079680000001</v>
+        <v>7841.060864</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7954.868736</v>
+        <v>7910.429696</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>43.57</v>
+        <v>41.98</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18358.2208</v>
+        <v>17688.272896</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17564.93824</v>
+        <v>17590.218752</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>33.76</v>
+        <v>34.2</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>24877.524992</v>
+        <v>25201.760256</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>24217.030656</v>
+        <v>23590.672384</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.46</v>
+        <v>14.52</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10369.21344</v>
+        <v>9738.743807999999</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10047.264768</v>
+        <v>9416.795136000001</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.91</v>
+        <v>14.79</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16395.804672</v>
+        <v>15241.60512</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16482.225152</v>
+        <v>16389.118976</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.96</v>
+        <v>7.49</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2356.707584</v>
+        <v>2217.5552</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.48</v>
+        <v>8.23</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2569.078528</v>
+        <v>2493.339136</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2169.87776</v>
+        <v>2094.13824</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.33</v>
+        <v>8.82</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2063.81952</v>
+        <v>1951.006208</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1924.540672</v>
+        <v>1811.72736</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.72</v>
+        <v>26.33</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3973.654784</v>
+        <v>3774.39872</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.54309</v>
+        <v>4.541204</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3972.524032</v>
+        <v>3912.316928</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.93</v>
+        <v>5.51</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1039.35712</v>
+        <v>965.7433600000001</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>887.4140159999999</v>
+        <v>878.904704</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-16 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-17 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.88</v>
+        <v>15.81</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>41.98</v>
+        <v>41.77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34.2</v>
+        <v>32.75</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.52</v>
+        <v>14.33</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.79</v>
+        <v>14.35</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.49</v>
+        <v>7.41</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.23</v>
+        <v>8.16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.33</v>
+        <v>26.29</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>55.81</v>
+        <v>56.22</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-16 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-17 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.88</v>
+        <v>15.81</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7841.060864</v>
+        <v>7806.49728</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7910.429696</v>
+        <v>7436.41088</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>41.98</v>
+        <v>41.77</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17688.272896</v>
+        <v>17599.791104</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17590.218752</v>
+        <v>16831.789056</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34.2</v>
+        <v>32.75</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25201.760256</v>
+        <v>24133.26336</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23590.672384</v>
+        <v>22485.331968</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.52</v>
+        <v>14.33</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9738.743807999999</v>
+        <v>9611.308032000001</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.79</v>
+        <v>14.35</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15241.60512</v>
+        <v>14788.170752</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16389.118976</v>
+        <v>15230.467072</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.49</v>
+        <v>7.41</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2217.5552</v>
+        <v>2193.869824</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2367.107584</v>
+        <v>2227.9552</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.23</v>
+        <v>8.16</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2493.339136</v>
+        <v>2472.132096</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1951.006208</v>
+        <v>1973.126528</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>26.33</v>
+        <v>26.29</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3774.39872</v>
+        <v>3768.664832</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.541204</v>
+        <v>4.54309</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3912.316928</v>
+        <v>3707.326976</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>965.7433600000001</v>
+        <v>963.9906559999999</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>878.904704</v>
+        <v>807.426304</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-17 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-20 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.81</v>
+        <v>15.85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>41.77</v>
+        <v>42.19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>32.75</v>
+        <v>33.06</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.33</v>
+        <v>14.29</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.35</v>
+        <v>14.16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.16</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8.92</v>
+        <v>8.91</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.29</v>
+        <v>26</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>56.22</v>
+        <v>56.56</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-17 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-20 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.81</v>
+        <v>15.85</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7806.49728</v>
+        <v>7826.24768</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7436.41088</v>
+        <v>7421.597696</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>41.77</v>
+        <v>42.19</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17599.791104</v>
+        <v>17776.756736</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>32.75</v>
+        <v>33.06</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>24133.26336</v>
+        <v>24361.701376</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.33</v>
+        <v>14.29</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9611.308032000001</v>
+        <v>9584.480256000001</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9416.795136000001</v>
+        <v>9262.531584</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.35</v>
+        <v>14.16</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>14788.170752</v>
+        <v>14592.36864</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15230.467072</v>
+        <v>14578.725888</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2193.869824</v>
+        <v>2220.516096</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2227.9552</v>
+        <v>2202.469888</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.16</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2472.132096</v>
+        <v>2432.747776</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2094.13824</v>
+        <v>2033.54688</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.92</v>
+        <v>8.91</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1973.126528</v>
+        <v>1970.914432</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1811.72736</v>
+        <v>1831.635584</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>26.29</v>
+        <v>26</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3768.664832</v>
+        <v>3727.093248</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.54309</v>
+        <v>4.4966173</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>3707.326976</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>963.9906559999999</v>
+        <v>976.259648</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>807.426304</v>
+        <v>817.637504</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-20 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-21 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.85</v>
+        <v>16.87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42.19</v>
+        <v>44.43</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.06</v>
+        <v>34</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.29</v>
+        <v>15.29</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8.91</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26</v>
+        <v>27.11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.57</v>
+        <v>6.05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>56.56</v>
+        <v>59.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-20 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-21 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.85</v>
+        <v>16.87</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7826.24768</v>
+        <v>8329.892863999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>42.19</v>
+        <v>44.43</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17776.756736</v>
+        <v>18720.581632</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>16831.789056</v>
+        <v>17008.756736</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>33.06</v>
+        <v>34</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>24361.701376</v>
+        <v>25054.38208</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>22485.331968</v>
+        <v>22861.14816</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.29</v>
+        <v>15.29</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9584.480256000001</v>
+        <v>10255.192064</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9262.531584</v>
+        <v>9933.243392</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.16</v>
+        <v>15.3</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>14592.36864</v>
+        <v>15767.17824</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2220.516096</v>
+        <v>2427.764224</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2202.469888</v>
+        <v>2229.115904</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.029999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2432.747776</v>
+        <v>2566.049024</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2033.54688</v>
+        <v>2166.848</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.91</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1970.914432</v>
+        <v>2108.060032</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1831.635584</v>
+        <v>1968.781184</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>26</v>
+        <v>27.11</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3727.093248</v>
+        <v>3886.211584</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.4966173</v>
+        <v>4.4935155</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3707.326976</v>
+        <v>3665.755392</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.57</v>
+        <v>6.05</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>976.259648</v>
+        <v>1060.38976</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-21 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-22 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.87</v>
+        <v>17.31</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.43</v>
+        <v>45.29</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.29</v>
+        <v>15.69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.3</v>
+        <v>15.84</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.11</v>
+        <v>29.41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.05</v>
+        <v>6.26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>59.1</v>
+        <v>59.74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-21 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-22 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.87</v>
+        <v>17.31</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8329.892863999999</v>
+        <v>8547.150847999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7421.597696</v>
+        <v>8142.501376</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.43</v>
+        <v>45.29</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18720.581632</v>
+        <v>19082.942464</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17008.756736</v>
+        <v>17952.579584</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34</v>
+        <v>34.85</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25054.38208</v>
+        <v>25680.740352</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>22861.14816</v>
+        <v>23959.117824</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.29</v>
+        <v>15.69</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10255.192064</v>
+        <v>10523.476992</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.3</v>
+        <v>15.84</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15767.17824</v>
+        <v>16323.666944</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>14578.725888</v>
+        <v>16316.703744</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2427.764224</v>
+        <v>2469.213952</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2229.115904</v>
+        <v>2436.364288</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2566.049024</v>
+        <v>2608.462848</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.529999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2108.060032</v>
+        <v>2198.753024</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.11</v>
+        <v>29.41</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3886.211584</v>
+        <v>4215.916032</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.4935155</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3665.755392</v>
+        <v>3824.873728</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.05</v>
+        <v>6.26</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1060.38976</v>
+        <v>1097.196672</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>817.637504</v>
+        <v>935.0663039999999</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-22 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-23 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.31</v>
+        <v>16.45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.29</v>
+        <v>44.19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34.5</v>
+        <v>35.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.69</v>
+        <v>15.32</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.84</v>
+        <v>15.24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.34</v>
+        <v>7.91</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.609999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.94</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>29.41</v>
+        <v>28.06</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.26</v>
+        <v>5.69</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>59.74</v>
+        <v>57.85</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-22 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-23 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.31</v>
+        <v>16.45</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8547.150847999999</v>
+        <v>8122.509824</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8142.501376</v>
+        <v>7717.859328</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.29</v>
+        <v>44.19</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19082.942464</v>
+        <v>18619.457536</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17952.579584</v>
+        <v>18314.942464</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34.85</v>
+        <v>35.45</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25680.740352</v>
+        <v>26122.876928</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23959.117824</v>
+        <v>24659.167232</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.69</v>
+        <v>15.32</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10523.476992</v>
+        <v>10275.313664</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9933.243392</v>
+        <v>10201.52832</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.84</v>
+        <v>15.24</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16323.666944</v>
+        <v>15705.346048</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16316.703744</v>
+        <v>15695.996928</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.34</v>
+        <v>7.91</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2469.213952</v>
+        <v>2341.904128</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2436.364288</v>
+        <v>2477.81376</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.609999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2608.462848</v>
+        <v>2550.901248</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2166.848</v>
+        <v>2209.26208</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.94</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2198.753024</v>
+        <v>2127.968256</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1968.781184</v>
+        <v>2059.474176</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>29.41</v>
+        <v>28.06</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4215.916032</v>
+        <v>4022.393856</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.4935155</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3824.873728</v>
+        <v>4154.578176</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.26</v>
+        <v>5.69</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1097.196672</v>
+        <v>997.29216</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>935.0663039999999</v>
+        <v>838.059904</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-23 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-24 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.45</v>
+        <v>16.31</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.19</v>
+        <v>44.03</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.45</v>
+        <v>33.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.32</v>
+        <v>15.14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.24</v>
+        <v>15.13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.91</v>
+        <v>7.82</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.42</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>28.06</v>
+        <v>27.79</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.69</v>
+        <v>5.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.85</v>
+        <v>58.49</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-23 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-24 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.45</v>
+        <v>16.31</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8122.509824</v>
+        <v>8053.381632</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7717.859328</v>
+        <v>7648.731648</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.19</v>
+        <v>44.03</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18619.457536</v>
+        <v>18552.041472</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18314.942464</v>
+        <v>17851.455488</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.45</v>
+        <v>33.9</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26122.876928</v>
+        <v>24980.692992</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>24659.167232</v>
+        <v>23082.215424</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.32</v>
+        <v>15.14</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10275.313664</v>
+        <v>10154.586112</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10201.52832</v>
+        <v>9953.364992000001</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.24</v>
+        <v>15.13</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15705.346048</v>
+        <v>15591.9872</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15695.996928</v>
+        <v>15582.200832</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.91</v>
+        <v>7.82</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2341.904128</v>
+        <v>2315.258112</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2477.81376</v>
+        <v>2350.504192</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.42</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2550.901248</v>
+        <v>2590.285568</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2209.26208</v>
+        <v>2151.700224</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2127.968256</v>
+        <v>2132.392448</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2059.474176</v>
+        <v>1988.689408</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>28.06</v>
+        <v>27.79</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4022.393856</v>
+        <v>3983.689472</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.4935155</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4154.578176</v>
+        <v>3961.056</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.69</v>
+        <v>5.63</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>997.29216</v>
+        <v>986.775872</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>838.059904</v>
+        <v>827.848704</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-24 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-27 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.31</v>
+        <v>16.22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.03</v>
+        <v>44.13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.9</v>
+        <v>33.13</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.14</v>
+        <v>15.19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.13</v>
+        <v>15.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.82</v>
+        <v>7.94</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.550000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.79</v>
+        <v>29.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.63</v>
+        <v>5.69</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.49</v>
+        <v>58.71</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-24 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-27 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.31</v>
+        <v>16.22</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8053.381632</v>
+        <v>8008.94208</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.03</v>
+        <v>44.13</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18552.041472</v>
+        <v>18594.177024</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17851.455488</v>
+        <v>17784.041472</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>33.9</v>
+        <v>33.13</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>24980.692992</v>
+        <v>24413.284352</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23082.215424</v>
+        <v>22735.876096</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.14</v>
+        <v>15.19</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10154.586112</v>
+        <v>10188.121088</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9953.364992000001</v>
+        <v>9832.636415999999</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.13</v>
+        <v>15.36</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15591.9872</v>
+        <v>15829.010432</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.82</v>
+        <v>7.94</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2315.258112</v>
+        <v>2350.786304</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2350.504192</v>
+        <v>2323.85792</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.550000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2590.285568</v>
+        <v>2593.315328</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2151.700224</v>
+        <v>2191.084544</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.640000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2132.392448</v>
+        <v>2158.936832</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1988.689408</v>
+        <v>1993.113472</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.79</v>
+        <v>29.05</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3983.689472</v>
+        <v>4164.310016</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.4935155</v>
+        <v>4.520655</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3961.056</v>
+        <v>3922.351616</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.63</v>
+        <v>5.69</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>986.775872</v>
+        <v>997.29216</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-27 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-28 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.22</v>
+        <v>15.69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.13</v>
+        <v>43.23</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.13</v>
+        <v>34</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.19</v>
+        <v>14.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.36</v>
+        <v>14.91</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.94</v>
+        <v>7.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.56</v>
+        <v>8.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.76</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>29.05</v>
+        <v>27.42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.69</v>
+        <v>5.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.71</v>
+        <v>57.12</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-27 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-28 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.22</v>
+        <v>15.69</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8008.94208</v>
+        <v>7747.244544</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7648.731648</v>
+        <v>7604.292608</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.13</v>
+        <v>43.23</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18594.177024</v>
+        <v>18214.961152</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17784.041472</v>
+        <v>17826.174976</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>33.13</v>
+        <v>34</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>24413.284352</v>
+        <v>25054.38208</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>22735.876096</v>
+        <v>23443.294208</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.19</v>
+        <v>14.55</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10188.121088</v>
+        <v>9758.865408</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9832.636415999999</v>
+        <v>9436.916735999999</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.36</v>
+        <v>14.91</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15829.010432</v>
+        <v>15365.269504</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15582.200832</v>
+        <v>15820.138496</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.94</v>
+        <v>7.75</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2350.786304</v>
+        <v>2294.53312</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2323.85792</v>
+        <v>2303.133184</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.56</v>
+        <v>8.42</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2593.315328</v>
+        <v>2550.901248</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2191.084544</v>
+        <v>2151.700224</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.76</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2158.936832</v>
+        <v>2077.09184</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1993.113472</v>
+        <v>1937.812864</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>29.05</v>
+        <v>27.42</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4164.310016</v>
+        <v>3930.650112</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.520655</v>
+        <v>4.515166</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3922.351616</v>
+        <v>4102.97216</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.69</v>
+        <v>5.5</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>997.29216</v>
+        <v>963.9906559999999</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>827.848704</v>
+        <v>838.059904</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-28 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-29 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.69</v>
+        <v>15.22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43.23</v>
+        <v>42.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -641,7 +641,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.55</v>
+        <v>14.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.91</v>
+        <v>14.63</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.42</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.390000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.42</v>
+        <v>27.02</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.12</v>
+        <v>58.59</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-28 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-29 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.69</v>
+        <v>15.22</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7747.244544</v>
+        <v>7515.172864</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.864</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7604.292608</v>
+        <v>7110.52288</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>798.038016</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>43.23</v>
+        <v>42.55</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18214.961152</v>
+        <v>17928.441856</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17826.174976</v>
+        <v>17446.961152</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5074,7 +5074,7 @@
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23443.294208</v>
+        <v>23607.252992</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.55</v>
+        <v>14.15</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9758.865408</v>
+        <v>9490.580480000001</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.91</v>
+        <v>14.63</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15365.269504</v>
+        <v>15076.72064</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15820.138496</v>
+        <v>15064.945664</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2294.53312</v>
+        <v>2238.280192</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.42</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2550.901248</v>
+        <v>2535.753216</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
@@ -5240,11 +5240,9 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>2077.09184</v>
-      </c>
+        <v>9.130000000000001</v>
+      </c>
+      <c r="D10" s="13" t="n"/>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
@@ -5275,16 +5273,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.42</v>
+        <v>27.02</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3930.650112</v>
+        <v>3873.310208</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.515166</v>
+        <v>4.5272837</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4102.97216</v>
+        <v>3869.312</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5308,14 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>963.9906559999999</v>
-      </c>
+        <v>5.27</v>
+      </c>
+      <c r="D12" s="13" t="n"/>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>838.059904</v>
+        <v>766.5815679999999</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-29 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-30 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.22</v>
+        <v>15.69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42.55</v>
+        <v>44.03</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34</v>
+        <v>35.54</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.15</v>
+        <v>14.93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.63</v>
+        <v>15.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.56</v>
+        <v>7.77</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.130000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.02</v>
+        <v>28.68</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.27</v>
+        <v>5.53</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.59</v>
+        <v>59.29</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-29 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-30 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.22</v>
+        <v>15.69</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7515.172864</v>
+        <v>7747.244544</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>5.864</v>
+        <v>5.62</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>7110.52288</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>42.55</v>
+        <v>44.03</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17928.441856</v>
+        <v>18552.041472</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17446.961152</v>
+        <v>17160.44288</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34</v>
+        <v>35.54</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25054.38208</v>
+        <v>26189.197312</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23607.252992</v>
+        <v>23002.482688</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.15</v>
+        <v>14.93</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9490.580480000001</v>
+        <v>10013.735936</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9436.916735999999</v>
+        <v>9168.631808</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.63</v>
+        <v>15.4</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15076.72064</v>
+        <v>15870.231552</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15064.945664</v>
+        <v>15861.518336</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.56</v>
+        <v>7.77</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2238.280192</v>
+        <v>2300.454656</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.179</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2303.133184</v>
+        <v>2246.880256</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>204.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.369999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2535.753216</v>
+        <v>2656.936448</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2151.700224</v>
+        <v>2136.55232</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,14 +5240,14 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.130000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1937.812864</v>
+        <v>1880.30016</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5273,16 +5273,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.02</v>
+        <v>28.68</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3873.310208</v>
+        <v>4111.270656</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.5272837</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3869.312</v>
+        <v>3811.972096</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5308,14 +5308,14 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.27</v>
+        <v>5.53</v>
       </c>
       <c r="D12" s="13" t="n"/>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>766.5815679999999</v>
+        <v>810.83008</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-30 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-07-31 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.69</v>
+        <v>15.03</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.03</v>
+        <v>43.11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.93</v>
+        <v>14.12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.4</v>
+        <v>14.91</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.77</v>
+        <v>7.52</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.77</v>
+        <v>8.43</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>28.68</v>
+        <v>27.54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.53</v>
+        <v>5.33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>59.29</v>
+        <v>57.78</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-30 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-07-31 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.69</v>
+        <v>15.03</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7747.244544</v>
+        <v>7408.382464</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.62</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.03</v>
+        <v>43.11</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18552.041472</v>
+        <v>18164.400128</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17160.44288</v>
+        <v>17396.39808</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5074,7 +5074,7 @@
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23002.482688</v>
+        <v>23413.817344</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.93</v>
+        <v>14.12</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10013.735936</v>
+        <v>9470.45888</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9168.631808</v>
+        <v>9691.787264000001</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.4</v>
+        <v>14.91</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15870.231552</v>
+        <v>15365.269504</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
@@ -5170,13 +5170,13 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.77</v>
+        <v>7.52</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2300.454656</v>
+        <v>2227.006464</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>2.179</v>
+        <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>2246.880256</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.77</v>
+        <v>8.43</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2656.936448</v>
+        <v>2553.930752</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2136.55232</v>
+        <v>2257.735168</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,14 +5240,14 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.640000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1880.30016</v>
+        <v>1993.113472</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5273,16 +5273,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>28.68</v>
+        <v>27.54</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4111.270656</v>
+        <v>3947.852032</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.5272837</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3811.972096</v>
+        <v>3886.514176</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.53</v>
+        <v>5.33</v>
       </c>
       <c r="D12" s="13" t="n"/>
       <c r="E12" s="12" t="n">

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-31 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-03 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.03</v>
+        <v>15.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43.11</v>
+        <v>43.73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.54</v>
+        <v>33.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.12</v>
+        <v>14.43</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.91</v>
+        <v>15.56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.52</v>
+        <v>7.73</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.43</v>
+        <v>8.67</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.33</v>
+        <v>5.53</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.78</v>
+        <v>58.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-07-31 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-03 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,19 +4995,19 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.03</v>
+        <v>15.7</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7408.382464</v>
+        <v>7738.629632</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.62</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7110.52288</v>
+        <v>6900.402688</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>798.038016</v>
+        <v>942.211968</v>
       </c>
       <c r="H3" s="14">
         <f>IFERROR(C3/E3,"n/m")</f>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>43.11</v>
+        <v>43.73</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18164.400128</v>
+        <v>18425.636864</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.54</v>
+        <v>33.7</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26189.197312</v>
+        <v>24833.314816</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.12</v>
+        <v>14.43</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9470.45888</v>
+        <v>9678.380031999999</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9691.787264000001</v>
+        <v>9148.510208</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.91</v>
+        <v>15.56</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15365.269504</v>
+        <v>16035.11808</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15861.518336</v>
+        <v>15354.60864</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,19 +5170,19 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.52</v>
+        <v>7.73</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2227.006464</v>
+        <v>2289.1968</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2246.880256</v>
+        <v>2231.806464</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>204.5</v>
+        <v>281.5</v>
       </c>
       <c r="H8" s="14">
         <f>IFERROR(C8/E8,"n/m")</f>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.43</v>
+        <v>8.67</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2553.930752</v>
+        <v>2626.640384</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2257.735168</v>
+        <v>2154.729728</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,14 +5240,14 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1993.113472</v>
+        <v>1931.176704</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5279,7 +5279,7 @@
         <v>3947.852032</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.5272837</v>
+        <v>4.490997</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>3886.514176</v>
@@ -5308,14 +5308,14 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.33</v>
+        <v>5.53</v>
       </c>
       <c r="D12" s="13" t="n"/>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>810.83008</v>
+        <v>776.792768</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-03 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-04 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.7</v>
+        <v>16.49</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43.73</v>
+        <v>44.91</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.7</v>
+        <v>34.56</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.43</v>
+        <v>15.39</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.56</v>
+        <v>16.21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.73</v>
+        <v>8.33</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.67</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9.56</v>
+        <v>10.21</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.54</v>
+        <v>32.18</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.53</v>
+        <v>5.91</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.3</v>
+        <v>59.71</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-03 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-04 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.7</v>
+        <v>16.49</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7738.629632</v>
+        <v>8128.026112</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>5.62</v>
+        <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>6900.402688</v>
+        <v>7230.650368</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>43.73</v>
+        <v>44.91</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18425.636864</v>
+        <v>18922.829824</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17396.39808</v>
+        <v>17657.634816</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>33.7</v>
+        <v>34.56</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>24833.314816</v>
+        <v>25467.041792</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23413.817344</v>
+        <v>23144.114176</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>2581.615104</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.43</v>
+        <v>15.39</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9678.380031999999</v>
+        <v>10322.264064</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9148.510208</v>
+        <v>9356.43136</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>876.406016</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.56</v>
+        <v>16.21</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16035.11808</v>
+        <v>16704.963584</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15354.60864</v>
+        <v>16027.040768</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.73</v>
+        <v>8.33</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2289.1968</v>
+        <v>2466.883584</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2231.806464</v>
+        <v>2293.9968</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.67</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2626.640384</v>
+        <v>2741.764352</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2154.729728</v>
+        <v>2227.439616</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,14 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="D10" s="13" t="n"/>
+        <v>10.21</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>2258.477824</v>
+      </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1931.176704</v>
+        <v>1975.417216</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5273,13 +5275,13 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27.54</v>
+        <v>32.18</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3947.852032</v>
+        <v>4612.99456</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.490997</v>
+        <v>4.4915633</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>3886.514176</v>
@@ -5308,14 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="D12" s="13" t="n"/>
+        <v>5.91</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>1035.851712</v>
+      </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>776.792768</v>
+        <v>810.83008</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-04 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-05 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.49</v>
+        <v>17.61</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.91</v>
+        <v>48.24</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34.56</v>
+        <v>37.75</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.39</v>
+        <v>16.54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.21</v>
+        <v>17.43</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.33</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.050000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.21</v>
+        <v>10.82</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>32.18</v>
+        <v>35.12</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.91</v>
+        <v>6.48</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>59.71</v>
+        <v>62.33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-04 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-05 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.49</v>
+        <v>17.61</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8128.026112</v>
+        <v>8680.081408</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>6.02</v>
+        <v>5.62</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>7230.650368</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.91</v>
+        <v>48.24</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18922.829824</v>
+        <v>20325.924864</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17657.634816</v>
+        <v>18154.827776</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,13 +5065,13 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34.56</v>
+        <v>37.75</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25467.041792</v>
+        <v>27817.732096</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>6.287</v>
+        <v>6.951</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>23144.114176</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.39</v>
+        <v>16.54</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10322.264064</v>
+        <v>11093.583872</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.21</v>
+        <v>17.43</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16704.963584</v>
+        <v>17962.217472</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.33</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2466.883584</v>
+        <v>2653.454592</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2293.9968</v>
+        <v>2658.254592</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.050000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2741.764352</v>
+        <v>2908.390912</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.822</v>
@@ -5240,16 +5240,14 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>2258.477824</v>
-      </c>
+        <v>10.82</v>
+      </c>
+      <c r="D10" s="13" t="n"/>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1975.417216</v>
+        <v>2119.198848</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5273,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>32.18</v>
+        <v>35.12</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4612.99456</v>
+        <v>5034.442752</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.4915633</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3886.514176</v>
+        <v>4551.65696</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,11 +5308,9 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>1035.851712</v>
-      </c>
+        <v>6.48</v>
+      </c>
+      <c r="D12" s="13" t="n"/>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-05 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-07 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.61</v>
+        <v>17.28</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>48.24</v>
+        <v>48.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37.75</v>
+        <v>37.06</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16.54</v>
+        <v>15.86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.43</v>
+        <v>15.65</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.6</v>
+        <v>9.56</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.82</v>
+        <v>10.79</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>35.12</v>
+        <v>35.29</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.48</v>
+        <v>6.38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>62.33</v>
+        <v>61.94</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-05 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-07 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.61</v>
+        <v>17.28</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8680.081408</v>
+        <v>8517.422592000001</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>5.62</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7230.650368</v>
+        <v>8009.442304</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>48.24</v>
+        <v>48.05</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20325.924864</v>
+        <v>20245.868544</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18154.827776</v>
+        <v>19477.866496</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,19 +5065,19 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.75</v>
+        <v>37.56</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27817.732096</v>
+        <v>27677.722624</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>6.951</v>
+        <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23144.114176</v>
+        <v>26082.617344</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>2581.615104</v>
+        <v>4027.734016</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(C5/E5,"n/m")</f>
@@ -5100,19 +5100,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.54</v>
+        <v>15.86</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11093.583872</v>
+        <v>10654.246912</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9356.43136</v>
+        <v>10190.42304</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>876.406016</v>
+        <v>969.484992</v>
       </c>
       <c r="H6" s="14">
         <f>IFERROR(C6/E6,"n/m")</f>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.43</v>
+        <v>15.65</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17962.217472</v>
+        <v>16127.864832</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16027.040768</v>
+        <v>17961.576448</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1365.54496</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2653.454592</v>
+        <v>2614.955776</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2658.254592</v>
+        <v>2619.755776</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.6</v>
+        <v>9.56</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2908.390912</v>
+        <v>2896.27264</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>5.822</v>
+        <v>5.485</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2227.439616</v>
+        <v>2509.189888</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>675.673984</v>
@@ -5240,14 +5240,14 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.82</v>
+        <v>10.79</v>
       </c>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2119.198848</v>
+        <v>2247.496448</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5273,16 +5273,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>35.12</v>
+        <v>35.29</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5034.442752</v>
+        <v>5058.812416</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.4915633</v>
+        <v>4.5083694</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4551.65696</v>
+        <v>4997.474816</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5308,14 +5308,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="D12" s="13" t="n"/>
+        <v>6.38</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>1114.987776</v>
+      </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>810.83008</v>
+        <v>955.488704</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.28</v>
+        <v>18.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>48.05</v>
+        <v>51.22</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.86</v>
+        <v>16.85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.65</v>
+        <v>17.39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.83</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.56</v>
+        <v>10.39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.79</v>
+        <v>11.45</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>35.29</v>
+        <v>37.88</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.38</v>
+        <v>6.88</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.94</v>
+        <v>63.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.28</v>
+        <v>18.4</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8517.422592000001</v>
+        <v>9069.476864</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>5.62</v>
+        <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>8009.442304</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>48.05</v>
+        <v>51.22</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20245.868544</v>
+        <v>21581.54752</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.56</v>
+        <v>37.06</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27677.722624</v>
+        <v>27309.277184</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.86</v>
+        <v>16.85</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10654.246912</v>
+        <v>11301.504</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
@@ -5135,19 +5135,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.65</v>
+        <v>17.39</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16127.864832</v>
+        <v>17875.787776</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.065</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17961.576448</v>
+        <v>15740.199936</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1365.54496</v>
+        <v>1615.486976</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(C7/E7,"n/m")</f>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.83</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2614.955776</v>
+        <v>2825.218304</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2619.755776</v>
+        <v>2830.018304</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,19 +5205,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.56</v>
+        <v>10.39</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2896.27264</v>
+        <v>3074.997248</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>5.485</v>
+        <v>5.87</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2509.189888</v>
+        <v>2549.38752</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>675.673984</v>
+        <v>761.715008</v>
       </c>
       <c r="H9" s="14">
         <f>IFERROR(C9/E9,"n/m")</f>
@@ -5240,9 +5240,11 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="D10" s="13" t="n"/>
+        <v>11.45</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>2532.769024</v>
+      </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
@@ -5273,10 +5275,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>35.29</v>
+        <v>37.88</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5058.812416</v>
+        <v>5430.088704</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.5083694</v>
@@ -5308,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.38</v>
+        <v>6.88</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1114.987776</v>
+        <v>1205.864704</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-07 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-10 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>18.4</v>
+        <v>18.85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>51.22</v>
+        <v>51.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37.06</v>
+        <v>39.65</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16.85</v>
+        <v>17.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.39</v>
+        <v>18.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>10.24</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.39</v>
+        <v>10.73</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>11.45</v>
+        <v>12.21</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.88</v>
+        <v>38.86</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.88</v>
+        <v>7.31</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>63.8</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-07 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-10 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.4</v>
+        <v>18.85</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9069.476864</v>
+        <v>9291.285503999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8009.442304</v>
+        <v>8783.305727999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>51.22</v>
+        <v>51.8</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21581.54752</v>
+        <v>21825.931264</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>19477.866496</v>
+        <v>20813.54752</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.06</v>
+        <v>39.65</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27309.277184</v>
+        <v>29217.830912</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>26082.617344</v>
+        <v>27512.190976</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.85</v>
+        <v>17.55</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11301.504</v>
+        <v>11771.001856</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.833</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10190.42304</v>
+        <v>10855.474176</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,19 +5135,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.39</v>
+        <v>18.15</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17875.787776</v>
+        <v>18657.019904</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>10.065</v>
+        <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15740.199936</v>
+        <v>17536.671744</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1615.486976</v>
+        <v>1639.442048</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(C7/E7,"n/m")</f>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>9.539999999999999</v>
+        <v>10.24</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2825.218304</v>
+        <v>3032.519424</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
@@ -5205,19 +5205,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.39</v>
+        <v>10.73</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3074.997248</v>
+        <v>3175.6224</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>5.87</v>
+        <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2549.38752</v>
+        <v>2746.729216</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>761.715008</v>
+        <v>750.460032</v>
       </c>
       <c r="H9" s="14">
         <f>IFERROR(C9/E9,"n/m")</f>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.45</v>
+        <v>12.21</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2532.769024</v>
+        <v>2700.882944</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2247.496448</v>
+        <v>2393.48992</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.88</v>
+        <v>38.86</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5430.088704</v>
+        <v>5570.571264</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.5083694</v>
+        <v>4.4735394</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4997.474816</v>
+        <v>5368.750592</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.88</v>
+        <v>7.31</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1205.864704</v>
+        <v>1281.231232</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>955.488704</v>
+        <v>1113.762304</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-10 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-11 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>18.85</v>
+        <v>18.96</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>51.8</v>
+        <v>51.79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39.65</v>
+        <v>40.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.55</v>
+        <v>17.76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18.15</v>
+        <v>18.58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.24</v>
+        <v>10.59</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.73</v>
+        <v>10.83</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.21</v>
+        <v>12.61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.86</v>
+        <v>38.74</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.31</v>
+        <v>7.38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>66.04000000000001</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-10 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-11 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.85</v>
+        <v>18.96</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9291.285503999999</v>
+        <v>9345.504256</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>51.8</v>
+        <v>51.79</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21825.931264</v>
+        <v>21821.718528</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>20813.54752</v>
+        <v>21057.929216</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39.65</v>
+        <v>40.4</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29217.830912</v>
+        <v>29770.502144</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>27512.190976</v>
+        <v>28543.842304</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.55</v>
+        <v>17.76</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11771.001856</v>
+        <v>11911.852032</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>3.833</v>
+        <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10855.474176</v>
+        <v>11325.712384</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>18.15</v>
+        <v>18.58</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18657.019904</v>
+        <v>19099.031552</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17536.671744</v>
+        <v>18317.901824</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.24</v>
+        <v>10.59</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3032.519424</v>
+        <v>3136.169984</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2830.018304</v>
+        <v>3140.969984</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.73</v>
+        <v>10.83</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3175.6224</v>
+        <v>3205.218304</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2746.729216</v>
+        <v>2847.35488</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.21</v>
+        <v>12.61</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2700.882944</v>
+        <v>2789.363712</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2393.48992</v>
+        <v>2561.60384</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>264.372</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.86</v>
+        <v>38.74</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5570.571264</v>
+        <v>5553.369088</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.4735394</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5368.750592</v>
+        <v>5509.233152</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.31</v>
+        <v>7.38</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1281.231232</v>
+        <v>1293.50016</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-11 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-12 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>18.96</v>
+        <v>19.16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>51.79</v>
+        <v>52.38</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.4</v>
+        <v>40.11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.76</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18.58</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.59</v>
+        <v>10.61</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.83</v>
+        <v>10.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.61</v>
+        <v>12.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.74</v>
+        <v>39.09</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.38</v>
+        <v>7.14</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.93000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-11 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-12 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.96</v>
+        <v>19.16</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9345.504256</v>
+        <v>9444.08576</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8783.305727999999</v>
+        <v>8837.525503999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>51.79</v>
+        <v>52.38</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21821.718528</v>
+        <v>22070.315008</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21057.929216</v>
+        <v>21053.71648</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.4</v>
+        <v>40.11</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29770.502144</v>
+        <v>29556.801536</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28543.842304</v>
+        <v>28330.143744</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.76</v>
+        <v>18.1</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11911.852032</v>
+        <v>12139.894784</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11325.712384</v>
+        <v>11466.783744</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>18.58</v>
+        <v>18.8</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19099.031552</v>
+        <v>19325.175808</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>18317.901824</v>
+        <v>18759.913472</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.59</v>
+        <v>10.61</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3136.169984</v>
+        <v>3142.0928</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.83</v>
+        <v>10.84</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3205.218304</v>
+        <v>3208.17792</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2847.35488</v>
+        <v>2876.950528</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,19 +5240,19 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.61</v>
+        <v>12.1</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2789.363712</v>
+        <v>2676.59648</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2561.60384</v>
+        <v>2717.12768</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>264.372</v>
+        <v>309.139008</v>
       </c>
       <c r="H10" s="14">
         <f>IFERROR(C10/E10,"n/m")</f>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.74</v>
+        <v>39.09</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5553.369088</v>
+        <v>5603.541504</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.4735394</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5509.233152</v>
+        <v>5492.031488</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.38</v>
+        <v>7.14</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1293.50016</v>
+        <v>1251.435136</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1113.762304</v>
+        <v>1125.675392</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>53.995</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Raw Data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ratios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="AISC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AISC" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-12 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-13 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>19.16</v>
+        <v>18.78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>52.38</v>
+        <v>47.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.11</v>
+        <v>40.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>18.1</v>
+        <v>17.73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18.8</v>
+        <v>18.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.61</v>
+        <v>10.31</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.84</v>
+        <v>10.49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.1</v>
+        <v>11.78</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.09</v>
+        <v>37.44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.14</v>
+        <v>6.91</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>65.3</v>
+        <v>64.63</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-12 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-13 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.16</v>
+        <v>18.78</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9444.08576</v>
+        <v>9256.781824</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8837.525503999999</v>
+        <v>8748.802048</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>52.38</v>
+        <v>47.3</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>22070.315008</v>
+        <v>19929.856</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21053.71648</v>
+        <v>21302.31296</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>1946</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.11</v>
+        <v>40.25</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29556.801536</v>
+        <v>29659.96544</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28330.143744</v>
+        <v>29207.048192</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.1</v>
+        <v>17.73</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12139.894784</v>
+        <v>11910.454272</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11466.783744</v>
+        <v>11695.184896</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>18.8</v>
+        <v>18.45</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19325.175808</v>
+        <v>18965.4016</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>18759.913472</v>
+        <v>18986.059776</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.61</v>
+        <v>10.31</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3142.0928</v>
+        <v>3053.249792</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3140.969984</v>
+        <v>3146.8928</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.84</v>
+        <v>10.49</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3208.17792</v>
+        <v>3104.592896</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2876.950528</v>
+        <v>2879.910144</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.1</v>
+        <v>11.78</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2676.59648</v>
+        <v>2605.810176</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2717.12768</v>
+        <v>2604.31232</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.09</v>
+        <v>37.44</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5603.541504</v>
+        <v>5367.0144</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.4735394</v>
+        <v>4.4617996</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5492.031488</v>
+        <v>5542.203904</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>154.392992</v>
@@ -5310,19 +5310,19 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.14</v>
+        <v>6.91</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1251.435136</v>
+        <v>1207.61216</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.634</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1125.675392</v>
+        <v>1037.397952</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>53.995</v>
+        <v>57.199</v>
       </c>
       <c r="H12" s="14">
         <f>IFERROR(C12/E12,"n/m")</f>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-13 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-14 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.42</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>18.78</v>
+        <v>19.26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>47.3</v>
+        <v>47.42</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.25</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.73</v>
+        <v>18.37</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18.45</v>
+        <v>18.81</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.31</v>
+        <v>10.66</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.49</v>
+        <v>10.67</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>11.78</v>
+        <v>12.02</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.44</v>
+        <v>35.95</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.91</v>
+        <v>7.02</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.63</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-13 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-14 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.78</v>
+        <v>19.26</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9256.781824</v>
+        <v>9493.377023999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>47.3</v>
+        <v>47.42</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19929.856</v>
+        <v>19661.185024</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.25</v>
+        <v>39</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29659.96544</v>
+        <v>28738.848768</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>29207.048192</v>
+        <v>27666.937856</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.73</v>
+        <v>18.37</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11910.454272</v>
+        <v>12320.987136</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11695.184896</v>
+        <v>11446.6304</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>18.45</v>
+        <v>18.81</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18965.4016</v>
+        <v>19335.456768</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>18986.059776</v>
+        <v>18626.28352</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.31</v>
+        <v>10.66</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3053.249792</v>
+        <v>3156.900096</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3146.8928</v>
+        <v>3161.700096</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.49</v>
+        <v>10.67</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3104.592896</v>
+        <v>3157.865216</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2879.910144</v>
+        <v>2776.324864</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.78</v>
+        <v>12.02</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2605.810176</v>
+        <v>2658.899968</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2604.31232</v>
+        <v>2533.526272</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,19 +5275,19 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.44</v>
+        <v>35.95</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5367.0144</v>
+        <v>5153.42336</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.4617996</v>
+        <v>4.746783</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5542.203904</v>
+        <v>5295.255552</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>154.392992</v>
+        <v>208.356992</v>
       </c>
       <c r="H11" s="14">
         <f>IFERROR(C11/E11,"n/m")</f>
@@ -5310,13 +5310,13 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.91</v>
+        <v>7.02</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1207.61216</v>
+        <v>1230.40256</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>1.634</v>
+        <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>1037.397952</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-14 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-17 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -580,14 +580,14 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6.42</v>
+        <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>19.26</v>
+        <v>19.57</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>47.42</v>
+        <v>48.11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39</v>
+        <v>39.85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>18.37</v>
+        <v>18.82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18.81</v>
+        <v>19.31</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.66</v>
+        <v>10.14</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.67</v>
+        <v>10.77</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.02</v>
+        <v>11.92</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>35.95</v>
+        <v>36.95</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.02</v>
+        <v>7.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.81999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-14 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-17 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.26</v>
+        <v>19.57</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9493.377023999999</v>
+        <v>9646.17728</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8748.802048</v>
+        <v>8985.397247999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,19 +5030,19 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>47.42</v>
+        <v>48.11</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19661.185024</v>
+        <v>20271.149056</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21302.31296</v>
+        <v>18915.649536</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>1946</v>
+        <v>2124</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(C4/E4,"n/m")</f>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39</v>
+        <v>39.85</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>28738.848768</v>
+        <v>29365.20704</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>27666.937856</v>
+        <v>27295.102976</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.37</v>
+        <v>18.82</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12320.987136</v>
+        <v>12642.681856</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11446.6304</v>
+        <v>11876.56192</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>18.81</v>
+        <v>19.31</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19335.456768</v>
+        <v>19849.422848</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>18626.28352</v>
+        <v>18996.338688</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.66</v>
+        <v>10.14</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3156.900096</v>
+        <v>3002.905088</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.67</v>
+        <v>10.77</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3157.865216</v>
+        <v>3187.46112</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2776.324864</v>
+        <v>2829.59744</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.02</v>
+        <v>11.92</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2658.899968</v>
+        <v>2636.779264</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2533.526272</v>
+        <v>2586.615808</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,19 +5275,19 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>35.95</v>
+        <v>36.95</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5153.42336</v>
+        <v>5322.136064</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.746783</v>
+        <v>4.4683313</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5295.255552</v>
+        <v>5092.172288</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>208.356992</v>
+        <v>207.972992</v>
       </c>
       <c r="H11" s="14">
         <f>IFERROR(C11/E11,"n/m")</f>
@@ -5310,19 +5310,19 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.02</v>
+        <v>7.2</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1230.40256</v>
+        <v>1258.293376</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1037.397952</v>
+        <v>1056.080448</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>57.199</v>
+        <v>57.053</v>
       </c>
       <c r="H12" s="14">
         <f>IFERROR(C12/E12,"n/m")</f>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-17 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-18 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>19.57</v>
+        <v>18.48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>48.11</v>
+        <v>46.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39.85</v>
+        <v>40.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>18.82</v>
+        <v>17.95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>19.31</v>
+        <v>18.51</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.14</v>
+        <v>9.66</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.77</v>
+        <v>10.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>11.92</v>
+        <v>11.54</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.95</v>
+        <v>34.71</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.2</v>
+        <v>6.83</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>65.84999999999999</v>
+        <v>63.24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-17 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-18 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.57</v>
+        <v>18.48</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9646.17728</v>
+        <v>9108.909056</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8985.397247999999</v>
+        <v>9138.197504</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>48.11</v>
+        <v>46.6</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20271.149056</v>
+        <v>19634.909184</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18915.649536</v>
+        <v>19203.4304</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39.85</v>
+        <v>40.3</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29365.20704</v>
+        <v>29696.811008</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>27295.102976</v>
+        <v>28470.153216</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.82</v>
+        <v>17.95</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12642.681856</v>
+        <v>12058.244096</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11876.56192</v>
+        <v>12178.857984</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>19.31</v>
+        <v>18.51</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19849.422848</v>
+        <v>19027.07712</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>18996.338688</v>
+        <v>19510.306816</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.14</v>
+        <v>9.66</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3002.905088</v>
+        <v>2860.755712</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3161.700096</v>
+        <v>3007.705088</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.77</v>
+        <v>10.45</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3187.46112</v>
+        <v>3092.754432</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2829.59744</v>
+        <v>2859.193088</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.92</v>
+        <v>11.54</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2636.779264</v>
+        <v>2552.72064</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2586.615808</v>
+        <v>2564.495104</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>36.95</v>
+        <v>34.71</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5322.136064</v>
+        <v>4999.495168</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.4683313</v>
+        <v>4.721012</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5092.172288</v>
+        <v>5236.20864</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.2</v>
+        <v>6.83</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1258.293376</v>
+        <v>1193.631104</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1056.080448</v>
+        <v>1086.651904</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-19 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>18.48</v>
+        <v>20.85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46.6</v>
+        <v>50.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.3</v>
+        <v>39.53</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.95</v>
+        <v>20.54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18.51</v>
+        <v>20.93</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>9.66</v>
+        <v>10.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.45</v>
+        <v>11.63</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>11.54</v>
+        <v>12.61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>34.71</v>
+        <v>37.58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.83</v>
+        <v>7.57</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>63.24</v>
+        <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-18 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-19 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.48</v>
+        <v>20.85</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9108.909056</v>
+        <v>10277.097472</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9138.197504</v>
+        <v>8600.930304</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>46.6</v>
+        <v>50.3</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19634.909184</v>
+        <v>20855.283712</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>19203.4304</v>
+        <v>18573.647872</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.3</v>
+        <v>39.53</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29696.811008</v>
+        <v>29129.402368</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28470.153216</v>
+        <v>27902.744576</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.95</v>
+        <v>20.54</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12058.244096</v>
+        <v>13776.433152</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>12178.857984</v>
+        <v>11594.4192</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>18.51</v>
+        <v>20.93</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19027.07712</v>
+        <v>21514.68032</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>19510.306816</v>
+        <v>18687.95904</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>9.66</v>
+        <v>10.99</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2860.755712</v>
+        <v>3254.62784</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3007.705088</v>
+        <v>2865.555712</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.45</v>
+        <v>11.63</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3092.754432</v>
+        <v>3441.984256</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2859.193088</v>
+        <v>2764.486656</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.54</v>
+        <v>12.61</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2552.72064</v>
+        <v>2789.411328</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.26</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2564.495104</v>
+        <v>2480.436736</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>34.71</v>
+        <v>37.58</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4999.495168</v>
+        <v>5412.87936</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.721012</v>
+        <v>4.7204227</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5236.20864</v>
+        <v>4913.567232</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.83</v>
+        <v>7.57</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1193.631104</v>
+        <v>1326.801664</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1086.651904</v>
+        <v>1023.810624</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-19 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-20 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>20.85</v>
+        <v>21.19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>50.3</v>
+        <v>51.92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39.53</v>
+        <v>42.86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20.54</v>
+        <v>20.82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>20.93</v>
+        <v>21.11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.99</v>
+        <v>10.97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>11.63</v>
+        <v>11.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.61</v>
+        <v>12.64</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.58</v>
+        <v>37.09</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.57</v>
+        <v>7.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>67</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-19 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-20 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.85</v>
+        <v>21.19</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10277.097472</v>
+        <v>10444.686336</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8600.930304</v>
+        <v>9769.117695999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>50.3</v>
+        <v>51.92</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20855.283712</v>
+        <v>21526.964224</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18573.647872</v>
+        <v>20116.822016</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39.53</v>
+        <v>42.86</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29129.402368</v>
+        <v>31583.258624</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.287</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>27902.744576</v>
+        <v>29302.843392</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.54</v>
+        <v>20.82</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13776.433152</v>
+        <v>13986.219008</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11594.4192</v>
+        <v>13334.299648</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.93</v>
+        <v>21.11</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21514.68032</v>
+        <v>21699.708928</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>18687.95904</v>
+        <v>21175.56224</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.99</v>
+        <v>10.97</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3254.62784</v>
+        <v>3248.705024</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2865.555712</v>
+        <v>3259.42784</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.63</v>
+        <v>11.9</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3441.984256</v>
+        <v>3521.892608</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2764.486656</v>
+        <v>3113.71648</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.61</v>
+        <v>12.64</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2789.411328</v>
+        <v>2796.047872</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.26</v>
+        <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2480.436736</v>
+        <v>2717.12768</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.58</v>
+        <v>37.09</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5412.87936</v>
+        <v>5342.301184</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7204227</v>
+        <v>4.7301335</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4913.567232</v>
+        <v>5326.951424</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.57</v>
+        <v>7.6</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1326.801664</v>
+        <v>1328.198656</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1023.810624</v>
+        <v>1149.49312</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-20 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-21 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>21.19</v>
+        <v>21.09</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>51.92</v>
+        <v>53.07</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>42.86</v>
+        <v>44</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20.82</v>
+        <v>20.72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.11</v>
+        <v>20.97</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.97</v>
+        <v>10.62</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>11.9</v>
+        <v>12.07</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.64</v>
+        <v>12.53</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.09</v>
+        <v>36.66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>68.26000000000001</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-20 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-21 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>21.19</v>
+        <v>21.09</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10444.686336</v>
+        <v>10395.395072</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9769.117695999999</v>
+        <v>9936.706560000001</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>51.92</v>
+        <v>53.07</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21526.964224</v>
+        <v>22003.775488</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>20116.822016</v>
+        <v>20792.481792</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>42.86</v>
+        <v>44</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>31583.258624</v>
+        <v>32423.317504</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>6.287</v>
+        <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>29302.843392</v>
+        <v>30356.600832</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.82</v>
+        <v>20.72</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13986.219008</v>
+        <v>13919.041536</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13334.299648</v>
+        <v>13522.395136</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>21.11</v>
+        <v>20.97</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21699.708928</v>
+        <v>21555.795968</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21175.56224</v>
+        <v>21360.5888</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1639.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.97</v>
+        <v>10.62</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3248.705024</v>
+        <v>3145.054464</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3259.42784</v>
+        <v>3253.505024</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.9</v>
+        <v>12.07</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3521.892608</v>
+        <v>3572.205312</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3113.71648</v>
+        <v>3193.624832</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.64</v>
+        <v>12.53</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2796.047872</v>
+        <v>2771.714816</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2717.12768</v>
+        <v>2723.763712</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.09</v>
+        <v>36.66</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5342.301184</v>
+        <v>5280.365568</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7301335</v>
+        <v>4.7000813</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5326.951424</v>
+        <v>5256.373248</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1328.198656</v>
+        <v>1256.929024</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1149.49312</v>
+        <v>1154.588288</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>
